--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -55862,31 +55862,31 @@
         <v>2.93</v>
       </c>
       <c r="AU254" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV254" t="n">
         <v>1</v>
       </c>
       <c r="AW254" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX254" t="n">
         <v>2</v>
       </c>
       <c r="AY254" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ254" t="n">
         <v>3</v>
       </c>
       <c r="BA254" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB254" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC254" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD254" t="n">
         <v>1.51</v>
@@ -56080,7 +56080,7 @@
         <v>3.43</v>
       </c>
       <c r="AU255" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV255" t="n">
         <v>3</v>
@@ -56092,7 +56092,7 @@
         <v>2</v>
       </c>
       <c r="AY255" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ255" t="n">
         <v>5</v>
@@ -56519,28 +56519,28 @@
         <v>7</v>
       </c>
       <c r="AV257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW257" t="n">
         <v>5</v>
       </c>
       <c r="AX257" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY257" t="n">
         <v>12</v>
       </c>
       <c r="AZ257" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA257" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB257" t="n">
         <v>2</v>
       </c>
       <c r="BC257" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD257" t="n">
         <v>1.95</v>

--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -55650,25 +55650,25 @@
         <v>4</v>
       </c>
       <c r="AW253" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX253" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AY253" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA253" t="n">
         <v>7</v>
       </c>
-      <c r="AZ253" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA253" t="n">
-        <v>6</v>
-      </c>
       <c r="BB253" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC253" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD253" t="n">
         <v>3.06</v>
@@ -55862,22 +55862,22 @@
         <v>2.93</v>
       </c>
       <c r="AU254" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV254" t="n">
         <v>1</v>
       </c>
       <c r="AW254" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX254" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AY254" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ254" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="BA254" t="n">
         <v>6</v>
@@ -56083,16 +56083,16 @@
         <v>5</v>
       </c>
       <c r="AV255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX255" t="n">
         <v>3</v>
       </c>
-      <c r="AW255" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX255" t="n">
-        <v>2</v>
-      </c>
       <c r="AY255" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AZ255" t="n">
         <v>5</v>
@@ -56298,22 +56298,22 @@
         <v>3.76</v>
       </c>
       <c r="AU256" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX256" t="n">
         <v>9</v>
       </c>
-      <c r="AV256" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW256" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX256" t="n">
-        <v>4</v>
-      </c>
       <c r="AY256" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ256" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BA256" t="n">
         <v>7</v>
@@ -56519,19 +56519,19 @@
         <v>7</v>
       </c>
       <c r="AV257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW257" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AX257" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY257" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ257" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA257" t="n">
         <v>4</v>
@@ -56734,22 +56734,22 @@
         <v>3.61</v>
       </c>
       <c r="AU258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV258" t="n">
         <v>4</v>
       </c>
       <c r="AW258" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX258" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY258" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ258" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA258" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP258"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.43</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.07</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.67</v>
@@ -6146,7 +6146,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR26" t="n">
         <v>1.43</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.85</v>
@@ -7018,7 +7018,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR30" t="n">
         <v>1.67</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.17</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.23</v>
@@ -9416,7 +9416,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR41" t="n">
         <v>1.79</v>
@@ -10067,7 +10067,7 @@
         <v>2</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.23</v>
@@ -10506,7 +10506,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR46" t="n">
         <v>1.21</v>
@@ -11375,7 +11375,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.67</v>
@@ -11596,7 +11596,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR51" t="n">
         <v>1.78</v>
@@ -11811,7 +11811,7 @@
         <v>3</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.23</v>
@@ -12250,7 +12250,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR54" t="n">
         <v>2.06</v>
@@ -13337,7 +13337,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.07</v>
@@ -16607,10 +16607,10 @@
         <v>1.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -16828,7 +16828,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR75" t="n">
         <v>2.02</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.21</v>
@@ -17264,7 +17264,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR77" t="n">
         <v>1.51</v>
@@ -17479,7 +17479,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.38</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.67</v>
@@ -20752,7 +20752,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR93" t="n">
         <v>1.12</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.43</v>
@@ -21188,7 +21188,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR95" t="n">
         <v>1.47</v>
@@ -21621,7 +21621,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ97" t="n">
         <v>2.08</v>
@@ -21842,7 +21842,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR98" t="n">
         <v>1.85</v>
@@ -24894,7 +24894,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR112" t="n">
         <v>2.04</v>
@@ -25109,7 +25109,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.31</v>
@@ -25330,7 +25330,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR114" t="n">
         <v>1.74</v>
@@ -25766,7 +25766,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR116" t="n">
         <v>1.87</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ118" t="n">
         <v>2.08</v>
@@ -26853,7 +26853,7 @@
         <v>1.6</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.38</v>
@@ -29036,7 +29036,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR131" t="n">
         <v>1.57</v>
@@ -29251,7 +29251,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.23</v>
@@ -29469,7 +29469,7 @@
         <v>2</v>
       </c>
       <c r="AP133" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.08</v>
@@ -30562,7 +30562,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR138" t="n">
         <v>1.42</v>
@@ -30780,7 +30780,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR139" t="n">
         <v>1.36</v>
@@ -31867,7 +31867,7 @@
         <v>1.29</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.23</v>
@@ -32960,7 +32960,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR149" t="n">
         <v>1.72</v>
@@ -34265,10 +34265,10 @@
         <v>1.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR155" t="n">
         <v>1.71</v>
@@ -34919,7 +34919,7 @@
         <v>1.29</v>
       </c>
       <c r="AP158" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.23</v>
@@ -35576,7 +35576,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR161" t="n">
         <v>1.39</v>
@@ -37317,10 +37317,10 @@
         <v>0.75</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR169" t="n">
         <v>1.6</v>
@@ -37538,7 +37538,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR170" t="n">
         <v>2.06</v>
@@ -38843,7 +38843,7 @@
         <v>0.63</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.58</v>
@@ -39933,10 +39933,10 @@
         <v>0.38</v>
       </c>
       <c r="AP181" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR181" t="n">
         <v>1.42</v>
@@ -40369,7 +40369,7 @@
         <v>1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.21</v>
@@ -40808,7 +40808,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR185" t="n">
         <v>2.14</v>
@@ -41680,7 +41680,7 @@
         <v>1</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR189" t="n">
         <v>1.35</v>
@@ -44075,7 +44075,7 @@
         <v>1.11</v>
       </c>
       <c r="AP200" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ200" t="n">
         <v>1.17</v>
@@ -44514,7 +44514,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR202" t="n">
         <v>1.7</v>
@@ -45386,7 +45386,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR206" t="n">
         <v>1.86</v>
@@ -45604,7 +45604,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR207" t="n">
         <v>2.01</v>
@@ -45819,7 +45819,7 @@
         <v>0.8</v>
       </c>
       <c r="AP208" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.85</v>
@@ -46037,7 +46037,7 @@
         <v>1.78</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.67</v>
@@ -47566,7 +47566,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR216" t="n">
         <v>1.64</v>
@@ -47999,7 +47999,7 @@
         <v>0.73</v>
       </c>
       <c r="AP218" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ218" t="n">
         <v>0.85</v>
@@ -48871,7 +48871,7 @@
         <v>0.91</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ222" t="n">
         <v>0.85</v>
@@ -49310,7 +49310,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ224" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR224" t="n">
         <v>1.7</v>
@@ -49964,7 +49964,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR227" t="n">
         <v>1.54</v>
@@ -50833,7 +50833,7 @@
         <v>1.73</v>
       </c>
       <c r="AP231" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ231" t="n">
         <v>1.43</v>
@@ -52798,7 +52798,7 @@
         <v>1</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR240" t="n">
         <v>1.34</v>
@@ -53013,7 +53013,7 @@
         <v>1.33</v>
       </c>
       <c r="AP241" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ241" t="n">
         <v>1.21</v>
@@ -53449,7 +53449,7 @@
         <v>0.25</v>
       </c>
       <c r="AP243" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.23</v>
@@ -53888,7 +53888,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ245" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR245" t="n">
         <v>1.82</v>
@@ -54542,7 +54542,7 @@
         <v>1</v>
       </c>
       <c r="AQ248" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR248" t="n">
         <v>1.32</v>
@@ -55763,7 +55763,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
@@ -56798,6 +56798,660 @@
       </c>
       <c r="BP258" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>8205981</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>46082.39583333334</v>
+      </c>
+      <c r="F259" t="n">
+        <v>26</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Waldhof Mannheim</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>1</v>
+      </c>
+      <c r="K259" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" t="n">
+        <v>2</v>
+      </c>
+      <c r="M259" t="n">
+        <v>1</v>
+      </c>
+      <c r="N259" t="n">
+        <v>3</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>['51', '56']</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R259" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S259" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T259" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U259" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V259" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W259" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X259" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ259" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX259" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY259" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA259" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB259" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC259" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE259" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF259" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG259" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH259" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI259" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ259" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK259" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL259" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM259" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN259" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO259" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BP259" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>8206116</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>46082.52083333334</v>
+      </c>
+      <c r="F260" t="n">
+        <v>26</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>MSV Duisburg</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Havelse</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" t="n">
+        <v>1</v>
+      </c>
+      <c r="L260" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" t="n">
+        <v>1</v>
+      </c>
+      <c r="N260" t="n">
+        <v>2</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R260" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S260" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U260" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V260" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W260" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X260" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU260" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX260" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY260" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ260" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA260" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB260" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC260" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE260" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF260" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG260" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH260" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI260" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM260" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN260" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO260" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP260" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>8205926</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>46082.64583333334</v>
+      </c>
+      <c r="F261" t="n">
+        <v>26</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Schweinfurt</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>2</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>2</v>
+      </c>
+      <c r="L261" t="n">
+        <v>2</v>
+      </c>
+      <c r="M261" t="n">
+        <v>2</v>
+      </c>
+      <c r="N261" t="n">
+        <v>4</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>['30', '43']</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>['87', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="R261" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S261" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T261" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U261" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V261" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W261" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X261" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AQ261" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU261" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV261" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX261" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY261" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA261" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB261" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC261" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BE261" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF261" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BG261" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH261" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BI261" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM261" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN261" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO261" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP261" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.57</v>
@@ -1786,7 +1786,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>2.08</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.23</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.21</v>
@@ -5928,7 +5928,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR25" t="n">
         <v>2.03</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.71</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.43</v>
@@ -7236,7 +7236,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR31" t="n">
         <v>1.73</v>
@@ -7454,7 +7454,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
         <v>1.5</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.23</v>
@@ -8108,7 +8108,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR35" t="n">
         <v>0.78</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.07</v>
@@ -8762,7 +8762,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR38" t="n">
         <v>1.12</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.23</v>
@@ -10503,7 +10503,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.71</v>
@@ -10724,7 +10724,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR47" t="n">
         <v>2.17</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.67</v>
@@ -11378,7 +11378,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR50" t="n">
         <v>1.53</v>
@@ -11593,7 +11593,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.54</v>
@@ -12032,7 +12032,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR53" t="n">
         <v>2.08</v>
@@ -12247,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.57</v>
@@ -12468,7 +12468,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR55" t="n">
         <v>1.64</v>
@@ -13122,7 +13122,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR58" t="n">
         <v>1.95</v>
@@ -14427,10 +14427,10 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR64" t="n">
         <v>1.38</v>
@@ -15081,10 +15081,10 @@
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR67" t="n">
         <v>1.59</v>
@@ -15299,10 +15299,10 @@
         <v>2</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR68" t="n">
         <v>1.87</v>
@@ -15735,10 +15735,10 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR70" t="n">
         <v>1.7</v>
@@ -15953,10 +15953,10 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR71" t="n">
         <v>1.86</v>
@@ -18354,7 +18354,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR82" t="n">
         <v>1.38</v>
@@ -18569,7 +18569,7 @@
         <v>1.25</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.23</v>
@@ -19008,7 +19008,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR85" t="n">
         <v>1.71</v>
@@ -19441,7 +19441,7 @@
         <v>0.75</v>
       </c>
       <c r="AP87" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.23</v>
@@ -19659,7 +19659,7 @@
         <v>1</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.21</v>
@@ -19877,10 +19877,10 @@
         <v>0.75</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR89" t="n">
         <v>1.8</v>
@@ -20095,10 +20095,10 @@
         <v>0.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR90" t="n">
         <v>1.48</v>
@@ -20316,7 +20316,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR91" t="n">
         <v>1.68</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.23</v>
@@ -23801,10 +23801,10 @@
         <v>1.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR107" t="n">
         <v>1.49</v>
@@ -24022,7 +24022,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR108" t="n">
         <v>1.62</v>
@@ -24237,10 +24237,10 @@
         <v>1.8</v>
       </c>
       <c r="AP109" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR109" t="n">
         <v>1.64</v>
@@ -24455,7 +24455,7 @@
         <v>2.2</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.23</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR111" t="n">
         <v>1.33</v>
@@ -25545,7 +25545,7 @@
         <v>0.67</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.85</v>
@@ -26420,7 +26420,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR119" t="n">
         <v>1.9</v>
@@ -27507,7 +27507,7 @@
         <v>1.17</v>
       </c>
       <c r="AP124" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.07</v>
@@ -27725,10 +27725,10 @@
         <v>2</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR125" t="n">
         <v>1.84</v>
@@ -27943,7 +27943,7 @@
         <v>1.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.23</v>
@@ -28164,7 +28164,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR127" t="n">
         <v>1.75</v>
@@ -29472,7 +29472,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR133" t="n">
         <v>1.4</v>
@@ -30123,10 +30123,10 @@
         <v>0.67</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR136" t="n">
         <v>1.74</v>
@@ -30341,7 +30341,7 @@
         <v>1.17</v>
       </c>
       <c r="AP137" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.67</v>
@@ -30777,7 +30777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.57</v>
@@ -31216,7 +31216,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR141" t="n">
         <v>2.03</v>
@@ -31652,7 +31652,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR143" t="n">
         <v>1.53</v>
@@ -32739,7 +32739,7 @@
         <v>1.14</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.21</v>
@@ -32957,7 +32957,7 @@
         <v>0.86</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.71</v>
@@ -33396,7 +33396,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR151" t="n">
         <v>1.79</v>
@@ -33614,7 +33614,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR152" t="n">
         <v>2</v>
@@ -34050,7 +34050,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR154" t="n">
         <v>1.67</v>
@@ -34483,7 +34483,7 @@
         <v>0.57</v>
       </c>
       <c r="AP156" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.31</v>
@@ -34704,7 +34704,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR157" t="n">
         <v>1.89</v>
@@ -35355,7 +35355,7 @@
         <v>2</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ160" t="n">
         <v>2.08</v>
@@ -35573,7 +35573,7 @@
         <v>0.43</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.54</v>
@@ -36012,7 +36012,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR163" t="n">
         <v>2.02</v>
@@ -36227,7 +36227,7 @@
         <v>1.13</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.23</v>
@@ -37099,7 +37099,7 @@
         <v>0.38</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.23</v>
@@ -37971,7 +37971,7 @@
         <v>1.75</v>
       </c>
       <c r="AP172" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ172" t="n">
         <v>2.08</v>
@@ -38189,7 +38189,7 @@
         <v>1.63</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.67</v>
@@ -38410,7 +38410,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR174" t="n">
         <v>1.52</v>
@@ -38628,7 +38628,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR175" t="n">
         <v>1.45</v>
@@ -38846,7 +38846,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR176" t="n">
         <v>1.66</v>
@@ -39279,7 +39279,7 @@
         <v>1.88</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.38</v>
@@ -39500,7 +39500,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR179" t="n">
         <v>1.98</v>
@@ -40154,7 +40154,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR182" t="n">
         <v>1.75</v>
@@ -40587,7 +40587,7 @@
         <v>1.33</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.07</v>
@@ -41459,7 +41459,7 @@
         <v>1.78</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.43</v>
@@ -42549,7 +42549,7 @@
         <v>1.2</v>
       </c>
       <c r="AP193" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.23</v>
@@ -42767,7 +42767,7 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.23</v>
@@ -42988,7 +42988,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR195" t="n">
         <v>2.1</v>
@@ -43203,7 +43203,7 @@
         <v>1.78</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.38</v>
@@ -43424,7 +43424,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR197" t="n">
         <v>1.62</v>
@@ -43857,7 +43857,7 @@
         <v>1.3</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.23</v>
@@ -44078,7 +44078,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR200" t="n">
         <v>1.48</v>
@@ -44296,7 +44296,7 @@
         <v>1</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR201" t="n">
         <v>1.42</v>
@@ -45822,7 +45822,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR208" t="n">
         <v>1.68</v>
@@ -46255,7 +46255,7 @@
         <v>1.11</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ210" t="n">
         <v>1.31</v>
@@ -46694,7 +46694,7 @@
         <v>1</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR212" t="n">
         <v>1.43</v>
@@ -47348,7 +47348,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR215" t="n">
         <v>1.74</v>
@@ -47563,7 +47563,7 @@
         <v>1.64</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ216" t="n">
         <v>1.57</v>
@@ -48002,7 +48002,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ218" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR218" t="n">
         <v>1.43</v>
@@ -48217,7 +48217,7 @@
         <v>1.45</v>
       </c>
       <c r="AP219" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ219" t="n">
         <v>1.23</v>
@@ -48435,7 +48435,7 @@
         <v>1.36</v>
       </c>
       <c r="AP220" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.07</v>
@@ -49528,7 +49528,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR225" t="n">
         <v>1.9</v>
@@ -49746,7 +49746,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR226" t="n">
         <v>1.38</v>
@@ -49961,7 +49961,7 @@
         <v>0.6</v>
       </c>
       <c r="AP227" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.54</v>
@@ -50179,7 +50179,7 @@
         <v>1.1</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ228" t="n">
         <v>1.31</v>
@@ -51054,7 +51054,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ232" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR232" t="n">
         <v>1.57</v>
@@ -51269,10 +51269,10 @@
         <v>1.18</v>
       </c>
       <c r="AP233" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR233" t="n">
         <v>1.87</v>
@@ -52362,7 +52362,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ238" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR238" t="n">
         <v>1.77</v>
@@ -52795,7 +52795,7 @@
         <v>1.58</v>
       </c>
       <c r="AP240" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ240" t="n">
         <v>1.57</v>
@@ -53231,7 +53231,7 @@
         <v>1.33</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ242" t="n">
         <v>1.23</v>
@@ -54321,7 +54321,7 @@
         <v>1.64</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ247" t="n">
         <v>1.38</v>
@@ -54539,7 +54539,7 @@
         <v>0.67</v>
       </c>
       <c r="AP248" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ248" t="n">
         <v>0.71</v>
@@ -54757,7 +54757,7 @@
         <v>1.82</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ249" t="n">
         <v>1.67</v>
@@ -54978,7 +54978,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR250" t="n">
         <v>1.68</v>
@@ -55196,7 +55196,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR251" t="n">
         <v>1.96</v>
@@ -57452,6 +57452,1096 @@
       </c>
       <c r="BP261" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>8205983</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>46084.625</v>
+      </c>
+      <c r="F262" t="n">
+        <v>27</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>1860 München</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Erzgebirge Aue</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" t="n">
+        <v>2</v>
+      </c>
+      <c r="L262" t="n">
+        <v>2</v>
+      </c>
+      <c r="M262" t="n">
+        <v>1</v>
+      </c>
+      <c r="N262" t="n">
+        <v>3</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>['7', '50']</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S262" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="T262" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U262" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V262" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W262" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X262" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ262" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU262" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA262" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB262" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC262" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD262" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE262" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF262" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG262" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH262" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BI262" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ262" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK262" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL262" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM262" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN262" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO262" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BP262" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>8205993</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>46084.625</v>
+      </c>
+      <c r="F263" t="n">
+        <v>27</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Osnabrück</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Viktoria Köln</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>2</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>2</v>
+      </c>
+      <c r="L263" t="n">
+        <v>2</v>
+      </c>
+      <c r="M263" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" t="n">
+        <v>2</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>['5', '42']</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R263" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S263" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T263" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V263" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W263" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X263" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ263" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY263" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA263" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB263" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC263" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE263" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF263" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BG263" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH263" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI263" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO263" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP263" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>8205991</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>46084.625</v>
+      </c>
+      <c r="F264" t="n">
+        <v>27</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Stuttgart II</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Energie Cottbus</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" t="n">
+        <v>2</v>
+      </c>
+      <c r="N264" t="n">
+        <v>3</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>['60', '64']</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R264" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S264" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T264" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U264" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V264" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="W264" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X264" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ264" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT264" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV264" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY264" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA264" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB264" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC264" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE264" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BF264" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BG264" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH264" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI264" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ264" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK264" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL264" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM264" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN264" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO264" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BP264" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>8205975</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>46084.625</v>
+      </c>
+      <c r="F265" t="n">
+        <v>27</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Hoffenheim II</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" t="n">
+        <v>2</v>
+      </c>
+      <c r="L265" t="n">
+        <v>1</v>
+      </c>
+      <c r="M265" t="n">
+        <v>3</v>
+      </c>
+      <c r="N265" t="n">
+        <v>4</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>['39', '78', '88']</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S265" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U265" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V265" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X265" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE265" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG265" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH265" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BI265" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM265" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN265" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO265" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP265" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>8205989</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>46084.625</v>
+      </c>
+      <c r="F266" t="n">
+        <v>27</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Verl</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Jahn Regensburg</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>2</v>
+      </c>
+      <c r="K266" t="n">
+        <v>2</v>
+      </c>
+      <c r="L266" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" t="n">
+        <v>2</v>
+      </c>
+      <c r="N266" t="n">
+        <v>3</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>['19', '35']</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R266" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S266" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U266" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V266" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X266" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI266" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP266"/>
+  <dimension ref="A1:BP271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.31</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2440,7 +2440,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.23</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.08</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.38</v>
@@ -4402,7 +4402,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.31</v>
@@ -5710,7 +5710,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR24" t="n">
         <v>0.23</v>
@@ -6797,10 +6797,10 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR29" t="n">
         <v>1.75</v>
@@ -7672,7 +7672,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR33" t="n">
         <v>2.52</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.54</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ37" t="n">
         <v>2.08</v>
@@ -8980,7 +8980,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR39" t="n">
         <v>1.95</v>
@@ -9198,7 +9198,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR40" t="n">
         <v>0.9399999999999999</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.57</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR43" t="n">
         <v>1.76</v>
@@ -10070,7 +10070,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR44" t="n">
         <v>1.55</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.85</v>
@@ -11160,7 +11160,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR49" t="n">
         <v>1.64</v>
@@ -11814,7 +11814,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR52" t="n">
         <v>1.45</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.85</v>
@@ -13555,7 +13555,7 @@
         <v>1.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ60" t="n">
         <v>2.08</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.21</v>
@@ -13991,10 +13991,10 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR62" t="n">
         <v>1.36</v>
@@ -14209,10 +14209,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR63" t="n">
         <v>1.94</v>
@@ -14645,10 +14645,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR65" t="n">
         <v>1.35</v>
@@ -14863,10 +14863,10 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR66" t="n">
         <v>1.8</v>
@@ -15517,10 +15517,10 @@
         <v>3</v>
       </c>
       <c r="AP69" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR69" t="n">
         <v>1.33</v>
@@ -18351,7 +18351,7 @@
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.54</v>
@@ -18572,7 +18572,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR83" t="n">
         <v>1.27</v>
@@ -18787,10 +18787,10 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR84" t="n">
         <v>1.23</v>
@@ -19223,10 +19223,10 @@
         <v>2.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR86" t="n">
         <v>1.44</v>
@@ -19444,7 +19444,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR87" t="n">
         <v>1.66</v>
@@ -20313,7 +20313,7 @@
         <v>2.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.23</v>
@@ -20534,7 +20534,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR92" t="n">
         <v>1.64</v>
@@ -21403,7 +21403,7 @@
         <v>0.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.85</v>
@@ -22714,7 +22714,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR102" t="n">
         <v>1.84</v>
@@ -22932,7 +22932,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR103" t="n">
         <v>1.78</v>
@@ -23147,7 +23147,7 @@
         <v>1.6</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.43</v>
@@ -23368,7 +23368,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR105" t="n">
         <v>1.31</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.21</v>
@@ -24019,7 +24019,7 @@
         <v>0.8</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.08</v>
@@ -24458,7 +24458,7 @@
         <v>2</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR110" t="n">
         <v>2</v>
@@ -24673,7 +24673,7 @@
         <v>0.2</v>
       </c>
       <c r="AP111" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ111" t="n">
         <v>1</v>
@@ -25763,7 +25763,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.71</v>
@@ -26638,7 +26638,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR120" t="n">
         <v>1.78</v>
@@ -27289,10 +27289,10 @@
         <v>1</v>
       </c>
       <c r="AP123" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR123" t="n">
         <v>1.34</v>
@@ -27946,7 +27946,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR126" t="n">
         <v>1.44</v>
@@ -28600,7 +28600,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR129" t="n">
         <v>1.89</v>
@@ -28815,10 +28815,10 @@
         <v>0.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR130" t="n">
         <v>1.66</v>
@@ -29033,7 +29033,7 @@
         <v>1</v>
       </c>
       <c r="AP131" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.71</v>
@@ -29254,7 +29254,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR132" t="n">
         <v>1.68</v>
@@ -29687,7 +29687,7 @@
         <v>1.5</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.38</v>
@@ -30344,7 +30344,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR137" t="n">
         <v>1.41</v>
@@ -30559,7 +30559,7 @@
         <v>0.33</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.54</v>
@@ -31434,7 +31434,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR142" t="n">
         <v>1.95</v>
@@ -31649,7 +31649,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ143" t="n">
         <v>1</v>
@@ -31870,7 +31870,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR144" t="n">
         <v>1.57</v>
@@ -32085,7 +32085,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.85</v>
@@ -32524,7 +32524,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR147" t="n">
         <v>1.9</v>
@@ -33393,7 +33393,7 @@
         <v>1.71</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.77</v>
@@ -33829,7 +33829,7 @@
         <v>1.71</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.38</v>
@@ -34701,7 +34701,7 @@
         <v>1.71</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.23</v>
@@ -34922,7 +34922,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR158" t="n">
         <v>1.38</v>
@@ -35140,7 +35140,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR159" t="n">
         <v>1.33</v>
@@ -35791,7 +35791,7 @@
         <v>1.38</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.07</v>
@@ -36230,7 +36230,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR164" t="n">
         <v>1.51</v>
@@ -36448,7 +36448,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR165" t="n">
         <v>1.75</v>
@@ -36881,7 +36881,7 @@
         <v>1.88</v>
       </c>
       <c r="AP167" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.43</v>
@@ -37102,7 +37102,7 @@
         <v>2</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR168" t="n">
         <v>1.75</v>
@@ -38192,7 +38192,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR173" t="n">
         <v>1.54</v>
@@ -38407,7 +38407,7 @@
         <v>0.88</v>
       </c>
       <c r="AP174" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.08</v>
@@ -38625,7 +38625,7 @@
         <v>1.5</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.23</v>
@@ -39061,7 +39061,7 @@
         <v>0.88</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.31</v>
@@ -39718,7 +39718,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -41023,7 +41023,7 @@
         <v>0.78</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ186" t="n">
         <v>0.85</v>
@@ -41244,7 +41244,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR187" t="n">
         <v>1.75</v>
@@ -41677,7 +41677,7 @@
         <v>1.56</v>
       </c>
       <c r="AP189" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.57</v>
@@ -41898,7 +41898,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR190" t="n">
         <v>1.99</v>
@@ -42116,7 +42116,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR191" t="n">
         <v>1.77</v>
@@ -42552,7 +42552,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR193" t="n">
         <v>1.32</v>
@@ -42770,7 +42770,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR194" t="n">
         <v>1.86</v>
@@ -43421,7 +43421,7 @@
         <v>1.67</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.77</v>
@@ -43639,7 +43639,7 @@
         <v>1.89</v>
       </c>
       <c r="AP198" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ198" t="n">
         <v>2.08</v>
@@ -43860,7 +43860,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR199" t="n">
         <v>1.49</v>
@@ -44293,7 +44293,7 @@
         <v>1.44</v>
       </c>
       <c r="AP201" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.23</v>
@@ -44729,7 +44729,7 @@
         <v>1.5</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.07</v>
@@ -45168,7 +45168,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR205" t="n">
         <v>1.75</v>
@@ -45383,7 +45383,7 @@
         <v>0.67</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.54</v>
@@ -46040,7 +46040,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR209" t="n">
         <v>1.63</v>
@@ -46691,7 +46691,7 @@
         <v>0.6</v>
       </c>
       <c r="AP212" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ212" t="n">
         <v>0.54</v>
@@ -47130,7 +47130,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR214" t="n">
         <v>1.64</v>
@@ -47781,7 +47781,7 @@
         <v>2</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ217" t="n">
         <v>2.08</v>
@@ -48220,7 +48220,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR219" t="n">
         <v>1.35</v>
@@ -48653,10 +48653,10 @@
         <v>1.36</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR221" t="n">
         <v>1.83</v>
@@ -49092,7 +49092,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ223" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR223" t="n">
         <v>1.85</v>
@@ -49525,7 +49525,7 @@
         <v>1.6</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ225" t="n">
         <v>1.77</v>
@@ -50400,7 +50400,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR229" t="n">
         <v>2</v>
@@ -50615,7 +50615,7 @@
         <v>1.7</v>
       </c>
       <c r="AP230" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ230" t="n">
         <v>1.38</v>
@@ -51487,7 +51487,7 @@
         <v>1</v>
       </c>
       <c r="AP234" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.31</v>
@@ -51923,7 +51923,7 @@
         <v>1.25</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ236" t="n">
         <v>1.07</v>
@@ -52144,7 +52144,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR237" t="n">
         <v>1.87</v>
@@ -52359,7 +52359,7 @@
         <v>0.92</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ238" t="n">
         <v>1</v>
@@ -52580,7 +52580,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR239" t="n">
         <v>1.8</v>
@@ -53234,7 +53234,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR242" t="n">
         <v>1.54</v>
@@ -53452,7 +53452,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR243" t="n">
         <v>1.69</v>
@@ -53670,7 +53670,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR244" t="n">
         <v>1.43</v>
@@ -53885,7 +53885,7 @@
         <v>0.55</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ245" t="n">
         <v>0.54</v>
@@ -54103,7 +54103,7 @@
         <v>1.58</v>
       </c>
       <c r="AP246" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.43</v>
@@ -54760,7 +54760,7 @@
         <v>2</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR249" t="n">
         <v>1.57</v>
@@ -57609,28 +57609,28 @@
         <v>4</v>
       </c>
       <c r="AV262" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW262" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX262" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AY262" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AZ262" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BA262" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB262" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BC262" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BD262" t="n">
         <v>1.64</v>
@@ -57824,31 +57824,31 @@
         <v>2.77</v>
       </c>
       <c r="AU263" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV263" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW263" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX263" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY263" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA263" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB263" t="n">
         <v>9</v>
       </c>
-      <c r="AZ263" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA263" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB263" t="n">
-        <v>7</v>
-      </c>
       <c r="BC263" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD263" t="n">
         <v>1.36</v>
@@ -58045,19 +58045,19 @@
         <v>5</v>
       </c>
       <c r="AV264" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX264" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AY264" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ264" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA264" t="n">
         <v>6</v>
@@ -58263,28 +58263,28 @@
         <v>5</v>
       </c>
       <c r="AV265" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW265" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX265" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY265" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ265" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA265" t="n">
         <v>4</v>
       </c>
       <c r="BB265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC265" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD265" t="n">
         <v>1.51</v>
@@ -58478,31 +58478,31 @@
         <v>3.54</v>
       </c>
       <c r="AU266" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV266" t="n">
         <v>4</v>
       </c>
       <c r="AW266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB266" t="n">
         <v>6</v>
       </c>
-      <c r="AX266" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY266" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ266" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA266" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB266" t="n">
-        <v>4</v>
-      </c>
       <c r="BC266" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD266" t="n">
         <v>1.35</v>
@@ -58542,6 +58542,1096 @@
       </c>
       <c r="BP266" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>8205786</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>46085.625</v>
+      </c>
+      <c r="F267" t="n">
+        <v>27</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Schweinfurt</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S267" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U267" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V267" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W267" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X267" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY267" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA267" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BE267" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="BI267" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM267" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN267" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO267" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP267" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>8205990</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>46085.625</v>
+      </c>
+      <c r="F268" t="n">
+        <v>27</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Rot-Weiss Essen</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Waldhof Mannheim</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>1</v>
+      </c>
+      <c r="L268" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R268" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S268" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="T268" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U268" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V268" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W268" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X268" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA268" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB268" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="BI268" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO268" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP268" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>8205927</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>46085.625</v>
+      </c>
+      <c r="F269" t="n">
+        <v>27</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>1</v>
+      </c>
+      <c r="L269" t="n">
+        <v>2</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>2</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>['30', '80']</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R269" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S269" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U269" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V269" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X269" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU269" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY269" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA269" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI269" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM269" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN269" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO269" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BP269" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>8205988</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>46085.625</v>
+      </c>
+      <c r="F270" t="n">
+        <v>27</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>MSV Duisburg</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R270" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S270" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U270" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V270" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W270" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X270" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU270" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY270" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA270" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB270" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC270" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BE270" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="BF270" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG270" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH270" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI270" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ270" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK270" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL270" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM270" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN270" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO270" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BP270" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>8205994</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>46085.625</v>
+      </c>
+      <c r="F271" t="n">
+        <v>27</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Havelse</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" t="n">
+        <v>2</v>
+      </c>
+      <c r="K271" t="n">
+        <v>3</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" t="n">
+        <v>3</v>
+      </c>
+      <c r="N271" t="n">
+        <v>4</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>['17', '30', '72']</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="R271" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S271" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T271" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U271" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V271" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="W271" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X271" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC271" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE271" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF271" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BG271" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI271" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ271" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BK271" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL271" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM271" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN271" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO271" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP271" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -58696,31 +58696,31 @@
         <v>2.89</v>
       </c>
       <c r="AU267" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW267" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX267" t="n">
         <v>4</v>
       </c>
       <c r="AY267" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ267" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA267" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB267" t="n">
         <v>0</v>
       </c>
       <c r="BC267" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD267" t="n">
         <v>1.26</v>
@@ -58914,31 +58914,31 @@
         <v>3.34</v>
       </c>
       <c r="AU268" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX268" t="n">
         <v>7</v>
       </c>
-      <c r="AV268" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW268" t="n">
+      <c r="AY268" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA268" t="n">
         <v>7</v>
-      </c>
-      <c r="AX268" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY268" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ268" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA268" t="n">
-        <v>5</v>
       </c>
       <c r="BB268" t="n">
         <v>3</v>
       </c>
       <c r="BC268" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD268" t="n">
         <v>1.67</v>
@@ -59135,7 +59135,7 @@
         <v>6</v>
       </c>
       <c r="AV269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW269" t="n">
         <v>13</v>
@@ -59147,7 +59147,7 @@
         <v>19</v>
       </c>
       <c r="AZ269" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA269" t="n">
         <v>9</v>
@@ -59350,31 +59350,31 @@
         <v>3.23</v>
       </c>
       <c r="AU270" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX270" t="n">
         <v>6</v>
       </c>
-      <c r="AV270" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW270" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX270" t="n">
-        <v>2</v>
-      </c>
       <c r="AY270" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ270" t="n">
         <v>6</v>
       </c>
       <c r="BA270" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB270" t="n">
         <v>2</v>
       </c>
       <c r="BC270" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD270" t="n">
         <v>2.13</v>
@@ -59568,31 +59568,31 @@
         <v>3.09</v>
       </c>
       <c r="AU271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV271" t="n">
         <v>9</v>
       </c>
       <c r="AW271" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX271" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY271" t="n">
         <v>7</v>
       </c>
-      <c r="AY271" t="n">
+      <c r="AZ271" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB271" t="n">
         <v>5</v>
       </c>
-      <c r="AZ271" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA271" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB271" t="n">
-        <v>3</v>
-      </c>
       <c r="BC271" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD271" t="n">
         <v>4.05</v>

--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP271"/>
+  <dimension ref="A1:BP278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.54</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.71</v>
@@ -2222,7 +2222,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.21</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.77</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.21</v>
@@ -5271,10 +5271,10 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
         <v>2.65</v>
@@ -5492,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR23" t="n">
         <v>1.3</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.21</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.77</v>
@@ -6582,7 +6582,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR28" t="n">
         <v>1.36</v>
@@ -6800,7 +6800,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR29" t="n">
         <v>1.75</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.54</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>1</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.21</v>
@@ -8326,7 +8326,7 @@
         <v>2</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
         <v>1.6</v>
@@ -8544,7 +8544,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR37" t="n">
         <v>0.77</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.14</v>
@@ -9416,7 +9416,7 @@
         <v>2</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR41" t="n">
         <v>1.79</v>
@@ -9631,10 +9631,10 @@
         <v>2</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
         <v>1.02</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.43</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.08</v>
@@ -10942,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR48" t="n">
         <v>1.3</v>
@@ -11160,7 +11160,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR49" t="n">
         <v>1.64</v>
@@ -11811,7 +11811,7 @@
         <v>3</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.21</v>
@@ -12029,7 +12029,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ53" t="n">
         <v>1</v>
@@ -12250,7 +12250,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR54" t="n">
         <v>2.06</v>
@@ -12465,7 +12465,7 @@
         <v>3</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.23</v>
@@ -12686,7 +12686,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR56" t="n">
         <v>1.16</v>
@@ -12904,7 +12904,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR57" t="n">
         <v>1.45</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.54</v>
@@ -13340,7 +13340,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR59" t="n">
         <v>1.37</v>
@@ -13558,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR60" t="n">
         <v>1.98</v>
@@ -14866,7 +14866,7 @@
         <v>2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR66" t="n">
         <v>1.8</v>
@@ -16171,10 +16171,10 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR72" t="n">
         <v>1.82</v>
@@ -16389,10 +16389,10 @@
         <v>1.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR73" t="n">
         <v>2.23</v>
@@ -16607,10 +16607,10 @@
         <v>1.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR74" t="n">
         <v>1.43</v>
@@ -16825,7 +16825,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.71</v>
@@ -17482,7 +17482,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR78" t="n">
         <v>1.28</v>
@@ -17697,7 +17697,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.43</v>
@@ -17915,10 +17915,10 @@
         <v>0.75</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR80" t="n">
         <v>1.85</v>
@@ -18133,10 +18133,10 @@
         <v>1.33</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR81" t="n">
         <v>1.48</v>
@@ -20534,7 +20534,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR92" t="n">
         <v>1.64</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.71</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.43</v>
@@ -21185,7 +21185,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.54</v>
@@ -21406,7 +21406,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR96" t="n">
         <v>1.77</v>
@@ -21624,7 +21624,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ97" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR97" t="n">
         <v>1.38</v>
@@ -21839,10 +21839,10 @@
         <v>1.75</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR98" t="n">
         <v>1.85</v>
@@ -22057,10 +22057,10 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR99" t="n">
         <v>1.98</v>
@@ -22275,10 +22275,10 @@
         <v>1</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR100" t="n">
         <v>1.97</v>
@@ -22493,10 +22493,10 @@
         <v>1</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR101" t="n">
         <v>1.83</v>
@@ -22711,7 +22711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.14</v>
@@ -24891,10 +24891,10 @@
         <v>1.4</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR112" t="n">
         <v>2.04</v>
@@ -25112,7 +25112,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR113" t="n">
         <v>1.44</v>
@@ -25327,7 +25327,7 @@
         <v>0.4</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.54</v>
@@ -25548,7 +25548,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR115" t="n">
         <v>1.66</v>
@@ -25981,10 +25981,10 @@
         <v>1.4</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR117" t="n">
         <v>1.08</v>
@@ -26199,10 +26199,10 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ118" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR118" t="n">
         <v>1.36</v>
@@ -26417,7 +26417,7 @@
         <v>0.6</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.54</v>
@@ -26635,10 +26635,10 @@
         <v>0.8</v>
       </c>
       <c r="AP120" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ120" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AQ120" t="n">
-        <v>1.77</v>
       </c>
       <c r="AR120" t="n">
         <v>1.78</v>
@@ -26856,7 +26856,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR121" t="n">
         <v>1.63</v>
@@ -27071,7 +27071,7 @@
         <v>1.33</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.21</v>
@@ -27510,7 +27510,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR124" t="n">
         <v>1.51</v>
@@ -28161,7 +28161,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ127" t="n">
         <v>1</v>
@@ -28597,7 +28597,7 @@
         <v>1.8</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.14</v>
@@ -29469,7 +29469,7 @@
         <v>2</v>
       </c>
       <c r="AP133" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.23</v>
@@ -29690,7 +29690,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR134" t="n">
         <v>1.91</v>
@@ -29905,10 +29905,10 @@
         <v>1.83</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ135" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR135" t="n">
         <v>1.77</v>
@@ -30344,7 +30344,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR137" t="n">
         <v>1.41</v>
@@ -30780,7 +30780,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR139" t="n">
         <v>1.36</v>
@@ -30995,10 +30995,10 @@
         <v>0.67</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR140" t="n">
         <v>1.17</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.08</v>
@@ -31431,7 +31431,7 @@
         <v>1.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.21</v>
@@ -32088,7 +32088,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR145" t="n">
         <v>1.35</v>
@@ -32303,7 +32303,7 @@
         <v>1.71</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.43</v>
@@ -33175,10 +33175,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR150" t="n">
         <v>1.81</v>
@@ -33611,7 +33611,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.54</v>
@@ -33832,7 +33832,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR153" t="n">
         <v>1.43</v>
@@ -34047,7 +34047,7 @@
         <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.08</v>
@@ -34268,7 +34268,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR155" t="n">
         <v>1.71</v>
@@ -34486,7 +34486,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR156" t="n">
         <v>1.32</v>
@@ -34919,7 +34919,7 @@
         <v>1.29</v>
       </c>
       <c r="AP158" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.14</v>
@@ -35137,10 +35137,10 @@
         <v>1.43</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR159" t="n">
         <v>1.33</v>
@@ -35358,7 +35358,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ160" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR160" t="n">
         <v>1.96</v>
@@ -35794,7 +35794,7 @@
         <v>2</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR162" t="n">
         <v>1.88</v>
@@ -36009,7 +36009,7 @@
         <v>0.88</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ163" t="n">
         <v>1</v>
@@ -36445,7 +36445,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.21</v>
@@ -36663,10 +36663,10 @@
         <v>0.5</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR166" t="n">
         <v>1.73</v>
@@ -37538,7 +37538,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR170" t="n">
         <v>2.06</v>
@@ -37753,7 +37753,7 @@
         <v>1</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.21</v>
@@ -37974,7 +37974,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ172" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR172" t="n">
         <v>1.33</v>
@@ -38192,7 +38192,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR173" t="n">
         <v>1.54</v>
@@ -39064,7 +39064,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR177" t="n">
         <v>1.94</v>
@@ -39282,7 +39282,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR178" t="n">
         <v>1.92</v>
@@ -39497,7 +39497,7 @@
         <v>1.88</v>
       </c>
       <c r="AP179" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.77</v>
@@ -39715,7 +39715,7 @@
         <v>1.5</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.14</v>
@@ -39933,7 +39933,7 @@
         <v>0.38</v>
       </c>
       <c r="AP181" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.54</v>
@@ -40151,7 +40151,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ182" t="n">
         <v>1</v>
@@ -40590,7 +40590,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR184" t="n">
         <v>1.53</v>
@@ -41026,7 +41026,7 @@
         <v>2</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR186" t="n">
         <v>1.89</v>
@@ -41241,7 +41241,7 @@
         <v>0.33</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.21</v>
@@ -41680,7 +41680,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR189" t="n">
         <v>1.35</v>
@@ -41895,7 +41895,7 @@
         <v>1.33</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.14</v>
@@ -42113,7 +42113,7 @@
         <v>1.33</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.21</v>
@@ -42331,7 +42331,7 @@
         <v>1</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.21</v>
@@ -43206,7 +43206,7 @@
         <v>2</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR196" t="n">
         <v>1.68</v>
@@ -43642,7 +43642,7 @@
         <v>1</v>
       </c>
       <c r="AQ198" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR198" t="n">
         <v>1.48</v>
@@ -44075,7 +44075,7 @@
         <v>1.11</v>
       </c>
       <c r="AP200" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ200" t="n">
         <v>1.08</v>
@@ -44511,7 +44511,7 @@
         <v>0.7</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.71</v>
@@ -44732,7 +44732,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR203" t="n">
         <v>1.97</v>
@@ -44947,10 +44947,10 @@
         <v>0.7</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR204" t="n">
         <v>1.77</v>
@@ -45165,7 +45165,7 @@
         <v>0.3</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.21</v>
@@ -45601,10 +45601,10 @@
         <v>1.5</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR207" t="n">
         <v>2.01</v>
@@ -46040,7 +46040,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR209" t="n">
         <v>1.63</v>
@@ -46258,7 +46258,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR210" t="n">
         <v>1.52</v>
@@ -46473,7 +46473,7 @@
         <v>1.9</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.43</v>
@@ -47127,7 +47127,7 @@
         <v>1.2</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.14</v>
@@ -47345,7 +47345,7 @@
         <v>1.3</v>
       </c>
       <c r="AP215" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.23</v>
@@ -47566,7 +47566,7 @@
         <v>2</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR216" t="n">
         <v>1.64</v>
@@ -47784,7 +47784,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ217" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR217" t="n">
         <v>1.7</v>
@@ -47999,7 +47999,7 @@
         <v>0.73</v>
       </c>
       <c r="AP218" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ218" t="n">
         <v>1</v>
@@ -48438,7 +48438,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR220" t="n">
         <v>1.89</v>
@@ -48874,7 +48874,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ222" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR222" t="n">
         <v>1.57</v>
@@ -49089,7 +49089,7 @@
         <v>0.27</v>
       </c>
       <c r="AP223" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.21</v>
@@ -49307,7 +49307,7 @@
         <v>0.64</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ224" t="n">
         <v>0.71</v>
@@ -49743,7 +49743,7 @@
         <v>1</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ226" t="n">
         <v>1.08</v>
@@ -50182,7 +50182,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR228" t="n">
         <v>1.47</v>
@@ -50397,10 +50397,10 @@
         <v>1.9</v>
       </c>
       <c r="AP229" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR229" t="n">
         <v>2</v>
@@ -50618,7 +50618,7 @@
         <v>1</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR230" t="n">
         <v>1.5</v>
@@ -51051,7 +51051,7 @@
         <v>0.55</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ232" t="n">
         <v>0.54</v>
@@ -51490,7 +51490,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR234" t="n">
         <v>1.44</v>
@@ -51708,7 +51708,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ235" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR235" t="n">
         <v>2.08</v>
@@ -51926,7 +51926,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR236" t="n">
         <v>1.74</v>
@@ -52141,7 +52141,7 @@
         <v>1.33</v>
       </c>
       <c r="AP237" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ237" t="n">
         <v>1.21</v>
@@ -52577,7 +52577,7 @@
         <v>1.36</v>
       </c>
       <c r="AP239" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ239" t="n">
         <v>1.14</v>
@@ -52798,7 +52798,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR240" t="n">
         <v>1.34</v>
@@ -53013,7 +53013,7 @@
         <v>1.33</v>
       </c>
       <c r="AP241" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ241" t="n">
         <v>1.21</v>
@@ -53667,7 +53667,7 @@
         <v>1.33</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.14</v>
@@ -54324,7 +54324,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ247" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR247" t="n">
         <v>1.58</v>
@@ -54760,7 +54760,7 @@
         <v>2</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR249" t="n">
         <v>1.57</v>
@@ -54975,7 +54975,7 @@
         <v>1.55</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ250" t="n">
         <v>1.77</v>
@@ -55193,7 +55193,7 @@
         <v>1</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ251" t="n">
         <v>1.08</v>
@@ -55411,10 +55411,10 @@
         <v>1.17</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR252" t="n">
         <v>1.88</v>
@@ -55629,10 +55629,10 @@
         <v>2</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ253" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR253" t="n">
         <v>1.62</v>
@@ -55847,10 +55847,10 @@
         <v>0.83</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR254" t="n">
         <v>1.53</v>
@@ -56065,7 +56065,7 @@
         <v>1.31</v>
       </c>
       <c r="AP255" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ255" t="n">
         <v>1.21</v>
@@ -56286,7 +56286,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ256" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR256" t="n">
         <v>2.02</v>
@@ -56501,10 +56501,10 @@
         <v>1.15</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR257" t="n">
         <v>1.54</v>
@@ -56719,7 +56719,7 @@
         <v>1.46</v>
       </c>
       <c r="AP258" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ258" t="n">
         <v>1.43</v>
@@ -56940,7 +56940,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR259" t="n">
         <v>1.52</v>
@@ -57373,7 +57373,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP261" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="AQ261" t="n">
         <v>0.71</v>
@@ -59556,7 +59556,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ271" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AR271" t="n">
         <v>1.46</v>
@@ -59632,6 +59632,1532 @@
       </c>
       <c r="BP271" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>8205996</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>46087.625</v>
+      </c>
+      <c r="F272" t="n">
+        <v>28</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Viktoria Köln</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>1860 München</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>1</v>
+      </c>
+      <c r="K272" t="n">
+        <v>1</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
+        <v>1</v>
+      </c>
+      <c r="N272" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>3</v>
+      </c>
+      <c r="R272" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S272" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T272" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U272" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V272" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W272" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X272" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY272" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA272" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB272" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC272" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE272" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF272" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BG272" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH272" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI272" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ272" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK272" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL272" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM272" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN272" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO272" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP272" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>8206109</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F273" t="n">
+        <v>28</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Erzgebirge Aue</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>2</v>
+      </c>
+      <c r="K273" t="n">
+        <v>2</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" t="n">
+        <v>3</v>
+      </c>
+      <c r="N273" t="n">
+        <v>4</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>['24', '27', '80']</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R273" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S273" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T273" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U273" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V273" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W273" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X273" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU273" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY273" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA273" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB273" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC273" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE273" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="BF273" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BG273" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH273" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BI273" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ273" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK273" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL273" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM273" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN273" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO273" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP273" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>8206117</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F274" t="n">
+        <v>28</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Energie Cottbus</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R274" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S274" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T274" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U274" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V274" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W274" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X274" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ274" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT274" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AU274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AY274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ274" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA274" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB274" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC274" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE274" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF274" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG274" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH274" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="BI274" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ274" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BK274" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL274" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM274" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN274" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO274" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP274" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>8205997</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F275" t="n">
+        <v>28</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Hoffenheim II</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Rot-Weiss Essen</t>
+        </is>
+      </c>
+      <c r="I275" t="n">
+        <v>1</v>
+      </c>
+      <c r="J275" t="n">
+        <v>1</v>
+      </c>
+      <c r="K275" t="n">
+        <v>2</v>
+      </c>
+      <c r="L275" t="n">
+        <v>2</v>
+      </c>
+      <c r="M275" t="n">
+        <v>4</v>
+      </c>
+      <c r="N275" t="n">
+        <v>6</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>['21', '66']</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>['45+1', '59', '76', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="R275" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S275" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T275" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U275" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V275" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W275" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X275" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ275" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT275" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AU275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV275" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX275" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY275" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ275" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA275" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB275" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC275" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE275" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="BF275" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG275" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH275" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BI275" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ275" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BK275" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL275" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM275" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN275" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO275" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP275" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>8206078</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F276" t="n">
+        <v>28</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Stuttgart II</t>
+        </is>
+      </c>
+      <c r="I276" t="n">
+        <v>2</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>2</v>
+      </c>
+      <c r="L276" t="n">
+        <v>2</v>
+      </c>
+      <c r="M276" t="n">
+        <v>1</v>
+      </c>
+      <c r="N276" t="n">
+        <v>3</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>['5', '16']</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R276" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S276" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T276" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U276" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V276" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W276" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X276" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AQ276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT276" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AU276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX276" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY276" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ276" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA276" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB276" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC276" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD276" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE276" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF276" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BG276" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH276" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI276" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ276" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK276" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL276" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM276" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN276" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO276" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BP276" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>8205992</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>46088.41666666666</v>
+      </c>
+      <c r="F277" t="n">
+        <v>28</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Schweinfurt</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="n">
+        <v>3</v>
+      </c>
+      <c r="M277" t="n">
+        <v>2</v>
+      </c>
+      <c r="N277" t="n">
+        <v>5</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>['73', '80', '90+4']</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>['48', '58']</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R277" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S277" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T277" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U277" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V277" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W277" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X277" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI277" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK277" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AO277" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ277" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR277" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS277" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT277" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV277" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ277" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA277" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB277" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC277" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD277" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BE277" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF277" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BG277" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH277" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI277" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ277" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK277" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL277" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM277" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN277" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO277" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP277" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>8206077</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>46088.52083333334</v>
+      </c>
+      <c r="F278" t="n">
+        <v>28</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Jahn Regensburg</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Osnabrück</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
+        <v>1</v>
+      </c>
+      <c r="K278" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
+        <v>2</v>
+      </c>
+      <c r="N278" t="n">
+        <v>2</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>['40', '63']</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R278" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S278" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T278" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U278" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V278" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W278" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X278" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI278" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK278" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN278" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO278" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP278" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ278" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR278" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS278" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT278" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AU278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY278" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ278" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA278" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB278" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC278" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD278" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE278" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="BF278" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BG278" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH278" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI278" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ278" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK278" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BL278" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM278" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN278" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO278" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP278" t="n">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 3. Liga_20252026.xlsx
@@ -60007,28 +60007,28 @@
         <v>4</v>
       </c>
       <c r="AV273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW273" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX273" t="n">
         <v>7</v>
       </c>
-      <c r="AX273" t="n">
-        <v>0</v>
-      </c>
       <c r="AY273" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ273" t="n">
         <v>11</v>
       </c>
-      <c r="AZ273" t="n">
-        <v>3</v>
-      </c>
       <c r="BA273" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB273" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC273" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD273" t="n">
         <v>1.89</v>
@@ -60225,19 +60225,19 @@
         <v>0</v>
       </c>
       <c r="AV274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW274" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX274" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY274" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AZ274" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BA274" t="n">
         <v>6</v>
@@ -60446,16 +60446,16 @@
         <v>7</v>
       </c>
       <c r="AW275" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX275" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY275" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AZ275" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BA275" t="n">
         <v>3</v>
@@ -60661,19 +60661,19 @@
         <v>4</v>
       </c>
       <c r="AV276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW276" t="n">
         <v>6</v>
       </c>
-      <c r="AW276" t="n">
-        <v>4</v>
-      </c>
       <c r="AX276" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY276" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ276" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA276" t="n">
         <v>5</v>
@@ -60876,31 +60876,31 @@
         <v>2.77</v>
       </c>
       <c r="AU277" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV277" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW277" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX277" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AY277" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ277" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BA277" t="n">
         <v>5</v>
       </c>
       <c r="BB277" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BC277" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BD277" t="n">
         <v>4.22</v>
@@ -61100,25 +61100,25 @@
         <v>3</v>
       </c>
       <c r="AW278" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX278" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AY278" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ278" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BA278" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB278" t="n">
         <v>5</v>
       </c>
       <c r="BC278" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD278" t="n">
         <v>1.85</v>
